--- a/evaluations/response_time_increasing_clients/4_DB/aggregated_workload.xlsx
+++ b/evaluations/response_time_increasing_clients/4_DB/aggregated_workload.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tuSemesters\Semester Winter 2022_23\Bachelor Thesis\sharded-distributed-databases\evaluations\response_time_increasing_clients\4_DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9DDDC3-E864-4B90-95BF-0CBA5877663A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2299F1B-6B17-4496-8277-E9507832ED67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>User Count</t>
   </si>
@@ -46,12 +46,15 @@
   <si>
     <t>Growth Rate Response Time</t>
   </si>
+  <si>
+    <t>Linear Growth Rate</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,6 +66,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -72,16 +76,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -113,11 +130,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -126,9 +159,14 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Output" xfId="1" builtinId="21"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -428,14 +466,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -448,8 +487,11 @@
       <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -463,8 +505,12 @@
         <f>C3/C2</f>
         <v>1.2410837936093131</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2">
+        <f>C3-C2</f>
+        <v>3.7223171588279289</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -478,8 +524,12 @@
         <f t="shared" ref="E3:E51" si="0">C4/C3</f>
         <v>1.2935730865878368</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3">
+        <f t="shared" ref="F3:F50" si="1">C4-C3</f>
+        <v>5.6255203626469203</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -493,8 +543,12 @@
         <f t="shared" si="0"/>
         <v>1.3258305015776017</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>8.0766110777531033</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -508,8 +562,12 @@
         <f t="shared" si="0"/>
         <v>1.1835184863842128</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>6.0312212154455551</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -523,8 +581,12 @@
         <f t="shared" si="0"/>
         <v>1.1543986163784496</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>6.005426961983332</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -538,8 +600,12 @@
         <f t="shared" si="0"/>
         <v>1.1536358412864109</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>6.8984071900162505</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -553,8 +619,12 @@
         <f t="shared" si="0"/>
         <v>1.1137657154191678</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>5.8929997868631006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -568,8 +638,12 @@
         <f t="shared" si="0"/>
         <v>1.1213286608344135</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>6.9997458591304564</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -583,8 +657,12 @@
         <f t="shared" si="0"/>
         <v>1.0839973218454522</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>5.4339699228728051</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -598,8 +676,12 @@
         <f t="shared" si="0"/>
         <v>1.1025829904247364</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>7.1937502375409679</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -613,8 +695,12 @@
         <f t="shared" si="0"/>
         <v>1.0779999382762724</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>6.0309474943897641</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -628,8 +714,12 @@
         <f t="shared" si="0"/>
         <v>1.0787483693451367</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>6.5637433912221326</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -643,8 +733,12 @@
         <f t="shared" si="0"/>
         <v>1.069163174040646</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>6.2187785575023042</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -658,8 +752,12 @@
         <f t="shared" si="0"/>
         <v>1.0739962722655134</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>7.1135110425440899</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -673,8 +771,12 @@
         <f t="shared" si="0"/>
         <v>1.0702849615498742</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>7.2567030853277998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -688,8 +790,12 @@
         <f t="shared" si="0"/>
         <v>1.0670545042357598</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17">
+        <f t="shared" si="1"/>
+        <v>7.4097630701070045</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -703,8 +809,12 @@
         <f t="shared" si="0"/>
         <v>1.0574096167473348</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18">
+        <f t="shared" si="1"/>
+        <v>6.7693600892727943</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -718,8 +828,12 @@
         <f t="shared" si="0"/>
         <v>1.0530334264384766</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19">
+        <f t="shared" si="1"/>
+        <v>6.6123512009957039</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -733,8 +847,12 @@
         <f t="shared" si="0"/>
         <v>1.0553955250306881</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20">
+        <f t="shared" si="1"/>
+        <v>7.2731587155278987</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -748,8 +866,12 @@
         <f t="shared" si="0"/>
         <v>1.0402014921501963</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21">
+        <f t="shared" si="1"/>
+        <v>5.5706491082576974</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -763,8 +885,12 @@
         <f t="shared" si="0"/>
         <v>1.0519512278844525</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22">
+        <f t="shared" si="1"/>
+        <v>7.4881911063851874</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -778,8 +904,12 @@
         <f t="shared" si="0"/>
         <v>1.0399115039711955</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23">
+        <f t="shared" si="1"/>
+        <v>6.051663916282223</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -793,8 +923,12 @@
         <f t="shared" si="0"/>
         <v>1.0436533951394675</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24">
+        <f t="shared" si="1"/>
+        <v>6.8832115406197829</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -808,8 +942,12 @@
         <f t="shared" si="0"/>
         <v>1.0410726615335175</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25">
+        <f t="shared" si="1"/>
+        <v>6.7589965826245191</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -823,8 +961,12 @@
         <f t="shared" si="0"/>
         <v>1.0410309716501225</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26">
+        <f t="shared" si="1"/>
+        <v>7.0294642119840773</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -838,8 +980,12 @@
         <f t="shared" si="0"/>
         <v>1.0388445665327575</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27">
+        <f t="shared" si="1"/>
+        <v>6.9279437447209204</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -853,8 +999,12 @@
         <f t="shared" si="0"/>
         <v>1.0343066176734925</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28">
+        <f t="shared" si="1"/>
+        <v>6.3562730951677793</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -868,8 +1018,12 @@
         <f t="shared" si="0"/>
         <v>1.0292030722729952</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29">
+        <f t="shared" si="1"/>
+        <v>5.5963193894958181</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -883,8 +1037,12 @@
         <f t="shared" si="0"/>
         <v>1.0333717045661672</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30">
+        <f t="shared" si="1"/>
+        <v>6.581932333932599</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -898,8 +1056,12 @@
         <f t="shared" si="0"/>
         <v>1.0330541986836719</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31">
+        <f t="shared" si="1"/>
+        <v>6.7368708524724923</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -913,8 +1075,12 @@
         <f t="shared" si="0"/>
         <v>1.0411125431494994</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32">
+        <f t="shared" si="1"/>
+        <v>8.656234998949202</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -928,8 +1094,12 @@
         <f t="shared" si="0"/>
         <v>1.0364464781461218</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <f t="shared" si="1"/>
+        <v>7.9892855362429884</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -943,8 +1113,12 @@
         <f t="shared" si="0"/>
         <v>1.0332841732122913</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34">
+        <f t="shared" si="1"/>
+        <v>7.5620061845248188</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -958,8 +1132,12 @@
         <f t="shared" si="0"/>
         <v>1.0325133716403911</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35">
+        <f t="shared" si="1"/>
+        <v>7.6327500430984969</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -973,8 +1151,12 @@
         <f t="shared" si="0"/>
         <v>1.0274133789927478</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36">
+        <f t="shared" si="1"/>
+        <v>6.6447292122665829</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -988,8 +1170,12 @@
         <f t="shared" si="0"/>
         <v>1.0274648367003585</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37">
+        <f t="shared" si="1"/>
+        <v>6.8396984492696049</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1003,8 +1189,12 @@
         <f t="shared" si="0"/>
         <v>1.0254494302473414</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <f t="shared" si="1"/>
+        <v>6.5118586571333026</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1018,8 +1208,12 @@
         <f t="shared" si="0"/>
         <v>1.023921098447832</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39">
+        <f t="shared" si="1"/>
+        <v>6.2765684291617276</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1033,8 +1227,12 @@
         <f t="shared" si="0"/>
         <v>1.0273410354313568</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40">
+        <f t="shared" si="1"/>
+        <v>7.3455209082301849</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1048,8 +1246,12 @@
         <f t="shared" si="0"/>
         <v>1.0326966978581311</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41">
+        <f t="shared" si="1"/>
+        <v>9.0245627969738962</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1063,8 +1265,12 @@
         <f t="shared" si="0"/>
         <v>1.0232550132394989</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F42">
+        <f t="shared" si="1"/>
+        <v>6.628444993430378</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1078,8 +1284,12 @@
         <f t="shared" si="0"/>
         <v>1.0230617981005135</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F43">
+        <f t="shared" si="1"/>
+        <v>6.7262361728097062</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1093,8 +1303,12 @@
         <f t="shared" si="0"/>
         <v>1.0238000819302522</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44">
+        <f t="shared" si="1"/>
+        <v>7.1016500354552932</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1108,8 +1322,12 @@
         <f t="shared" si="0"/>
         <v>1.0204433483289592</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45">
+        <f t="shared" si="1"/>
+        <v>6.2452237577876417</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1123,8 +1341,12 @@
         <f t="shared" si="0"/>
         <v>1.0222963837818355</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46">
+        <f t="shared" si="1"/>
+        <v>6.9505521294443611</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1138,8 +1360,12 @@
         <f t="shared" si="0"/>
         <v>1.0200854358568099</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47">
+        <f t="shared" si="1"/>
+        <v>6.4009282446018005</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1153,8 +1379,12 @@
         <f t="shared" si="0"/>
         <v>1.0227689505395232</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F48">
+        <f t="shared" si="1"/>
+        <v>7.401866689317842</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1168,8 +1398,12 @@
         <f t="shared" si="0"/>
         <v>1.0254082439758883</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F49">
+        <f t="shared" si="1"/>
+        <v>8.4479324276920806</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1184,7 +1418,7 @@
         <v>1.1032618731525046</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1194,15 +1428,14 @@
       <c r="C51">
         <v>376.14145063514081</v>
       </c>
-      <c r="E51">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E54" s="3">
-        <f>SUM(E2:E50)/49</f>
-        <v>1.0692944160625957</v>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E54" s="3"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F55" s="5">
+        <f>SUM(F2:F49)/48</f>
+        <v>6.7811635826729768</v>
       </c>
     </row>
   </sheetData>
